--- a/output/pdf_financials_xlsx/GRDM.xlsx
+++ b/output/pdf_financials_xlsx/GRDM.xlsx
@@ -1798,16 +1798,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.320354</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.036477</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.622579</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.573886</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>1.471993</v>
@@ -1816,19 +1816,19 @@
         <v>1.088604</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.895647</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>9.396673</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>2.717813</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.59676</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>2.804618</v>
       </c>
     </row>
     <row r="35">
@@ -1878,16 +1878,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.320354</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.036477</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.622579</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.08361200000000001</v>
+        <v>2.657498</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>1.530472</v>
@@ -1896,19 +1896,19 @@
         <v>1.138324</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.012147</v>
+        <v>2.907794</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>2.904164</v>
+        <v>12.300837</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.7553569999999999</v>
+        <v>3.47317</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.651392</v>
+        <v>1.248152</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.0599</v>
+        <v>2.864518</v>
       </c>
     </row>
     <row r="37">
@@ -2358,16 +2358,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.417258</v>
+        <v>0.096904</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.082705</v>
+        <v>0.046228</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.7007330000000001</v>
+        <v>0.078154</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.890686</v>
+        <v>0.3168</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.125254</v>
@@ -2376,19 +2376,19 @@
         <v>0.019608</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.91186</v>
+        <v>0.016213</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>9.727658999999999</v>
+        <v>0.330986</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.836774</v>
+        <v>0.118961</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.826278</v>
+        <v>0.229518</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>3.001622</v>
+        <v>0.197004</v>
       </c>
     </row>
     <row r="49">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -12080,7 +12080,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">

--- a/output/pdf_financials_xlsx/GRDM.xlsx
+++ b/output/pdf_financials_xlsx/GRDM.xlsx
@@ -649,37 +649,37 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>0.139678</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>0.07375</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.018754</v>
+        <v>0.096954</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.057382</v>
+        <v>0.222549</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.350764</v>
+        <v>0.6097630000000001</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.253597</v>
+        <v>0.506597</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.296485</v>
+        <v>0.616985</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.520353</v>
+        <v>0.766675</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.604226</v>
+        <v>1.704788</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.466452</v>
+        <v>1.234551</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.168186</v>
+        <v>1.289544</v>
       </c>
     </row>
     <row r="8">
@@ -769,37 +769,37 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.139678</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.07375</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.018754</v>
+        <v>0.096954</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.057382</v>
+        <v>0.222549</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.350764</v>
+        <v>0.6097630000000001</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.253597</v>
+        <v>0.506597</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.296485</v>
+        <v>0.616985</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.520353</v>
+        <v>0.766675</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.604226</v>
+        <v>1.704788</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.466452</v>
+        <v>1.234551</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.168186</v>
+        <v>1.289544</v>
       </c>
     </row>
     <row r="11">
@@ -809,37 +809,37 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-0.139678</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>-0.07375</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.018754</v>
+        <v>-0.096954</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.057382</v>
+        <v>-0.222549</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.350764</v>
+        <v>-0.6097630000000001</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.253597</v>
+        <v>-0.506597</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.296485</v>
+        <v>-0.616985</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.520353</v>
+        <v>-0.766675</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.604226</v>
+        <v>-1.704788</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.466452</v>
+        <v>-1.234551</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.168186</v>
+        <v>-1.289544</v>
       </c>
     </row>
     <row r="12">
@@ -4402,20 +4402,14 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.381999</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-2.601251</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-0.287774</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-0.033516</v>
@@ -4448,20 +4442,14 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>0</v>
@@ -4494,20 +4482,14 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0.07548100000000001</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>-0.059763</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0.056927</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>-0.5000830000000001</v>
@@ -4540,20 +4522,14 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E102" s="3" t="n">
         <v>0</v>
@@ -4586,20 +4562,14 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>-0.013554</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0.004895</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>0.0009700000000000001</v>
       </c>
       <c r="E103" s="3" t="n">
         <v>-0.309111</v>
@@ -4632,20 +4602,14 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.022648</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>1.218709</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>0.024892</v>
       </c>
       <c r="E104" s="3" t="n">
         <v>-0.319741</v>
@@ -4678,20 +4642,14 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E105" s="3" t="n">
         <v>0</v>
@@ -4724,20 +4682,14 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.084575</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>1.163841</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>0.082789</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>-1.128935</v>
@@ -4770,20 +4722,14 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E107" s="3" t="n">
         <v>0.534435</v>
@@ -4816,20 +4762,14 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E108" s="3" t="n">
         <v>0</v>
@@ -4862,20 +4802,14 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E109" s="3" t="n">
         <v>0</v>
@@ -4908,20 +4842,14 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>0</v>
@@ -4939,13 +4867,13 @@
         <v>0</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.135237</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.229271</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.020427</v>
       </c>
     </row>
     <row r="111">
@@ -4954,20 +4882,14 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -5000,20 +4922,14 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -5046,20 +4962,14 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E113" s="3" t="n">
         <v>0</v>
@@ -5092,20 +5002,14 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E114" s="3" t="n">
         <v>0</v>
@@ -5123,13 +5027,13 @@
         <v>0</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="L114" s="3" t="n">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="115">
@@ -5138,20 +5042,14 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0.09420000000000001</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -5163,19 +5061,19 @@
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.044755</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.9175410000000001</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>2.483932</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>1.043997</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>1.258894</v>
       </c>
     </row>
     <row r="116">
@@ -5184,20 +5082,14 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E116" s="3" t="n">
         <v>0</v>
@@ -5230,20 +5122,14 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E117" s="3" t="n">
         <v>0</v>
@@ -5276,20 +5162,14 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>-0.017034</v>
@@ -5322,20 +5202,14 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>0.023911</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>-0.1017</v>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>0.668254</v>
       </c>
       <c r="E119" s="3" t="n">
         <v>-0.017034</v>
@@ -5368,20 +5242,14 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E120" s="3" t="n">
         <v>0</v>
@@ -5414,20 +5282,14 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E121" s="3" t="n">
         <v>0</v>
@@ -5460,20 +5322,14 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E122" s="3" t="n">
         <v>0</v>
@@ -5506,20 +5362,14 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E123" s="3" t="n">
         <v>0</v>
@@ -5552,20 +5402,14 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
         <v>0</v>
@@ -5598,20 +5442,14 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
         <v>0</v>
@@ -5644,20 +5482,14 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E126" s="3" t="n">
         <v>0</v>
@@ -5752,20 +5584,14 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>-0.013835</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>-0.00409</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E128" s="3" t="n">
         <v>-0.273704</v>
@@ -5798,20 +5624,14 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>0.235737</v>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>0.124035</v>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E129" s="3" t="n">
         <v>3.42657</v>
@@ -5844,20 +5664,14 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0.26347</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>0.320354</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>0.036477</v>
       </c>
       <c r="E130" s="3" t="n">
         <v>0.622579</v>
@@ -5890,20 +5704,14 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E131" s="3" t="n">
         <v>0</v>
@@ -5936,20 +5744,14 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>0.056884</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>-0.283877</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>0.586102</v>
       </c>
       <c r="E132" s="3" t="n">
         <v>1.951307</v>
@@ -5982,20 +5784,14 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.320354</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>0.036477</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>0.622579</v>
       </c>
       <c r="E133" s="3" t="n">
         <v>2.573886</v>
@@ -6028,20 +5824,14 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -6074,20 +5864,14 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.202764</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>-0.306212</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>-0.082152</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-1.458229</v>
@@ -6125,7 +5909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O286"/>
+  <dimension ref="A1:O299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13329,20 +13113,14 @@
           <t>Amortization</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E103" s="5" t="n">
+        <v>0.00172</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>0.001254</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>0.000833</v>
       </c>
       <c r="H103" s="5" t="n">
         <v>0.0007</v>
@@ -13448,7 +13226,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -14280,7 +14062,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -14349,7 +14135,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -14491,7 +14281,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -15852,7 +15646,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -15917,7 +15715,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -16468,15 +16270,11 @@
           <t>NetOtherFinancingCharges</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E148" s="5" t="n">
+        <v>-0.013835</v>
+      </c>
+      <c r="F148" s="5" t="n">
+        <v>-0.00409</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -16609,15 +16407,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F150" s="5" t="n">
+        <v>-0.283877</v>
+      </c>
+      <c r="G150" s="5" t="n">
+        <v>0.586102</v>
       </c>
       <c r="H150" s="5" t="n">
         <v>1.951307</v>
@@ -16672,15 +16466,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F151" s="5" t="n">
+        <v>0.320354</v>
+      </c>
+      <c r="G151" s="5" t="n">
+        <v>0.036477</v>
       </c>
       <c r="H151" s="5" t="n">
         <v>0.622579</v>
@@ -16735,15 +16525,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F152" s="5" t="n">
+        <v>0.036477</v>
+      </c>
+      <c r="G152" s="5" t="n">
+        <v>0.622579</v>
       </c>
       <c r="H152" s="5" t="n">
         <v>2.573886</v>
@@ -16788,7 +16574,11 @@
           <t>Broker warrants issued in connection with the private placement (Note 9 (c)) $</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -17422,20 +17212,14 @@
           <t>ChangeInReceivables</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E162" s="5" t="n">
+        <v>0.07548100000000001</v>
+      </c>
+      <c r="F162" s="5" t="n">
+        <v>-0.059763</v>
+      </c>
+      <c r="G162" s="5" t="n">
+        <v>0.056927</v>
       </c>
       <c r="H162" s="5" t="n">
         <v>-0.5000830000000001</v>
@@ -17487,20 +17271,14 @@
           <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E163" s="5" t="n">
+        <v>-0.013554</v>
+      </c>
+      <c r="F163" s="5" t="n">
+        <v>0.004895</v>
+      </c>
+      <c r="G163" s="5" t="n">
+        <v>0.0009700000000000001</v>
       </c>
       <c r="H163" s="5" t="n">
         <v>-0.309111</v>
@@ -17552,20 +17330,14 @@
           <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E164" s="5" t="n">
+        <v>0.022648</v>
+      </c>
+      <c r="F164" s="5" t="n">
+        <v>1.218709</v>
+      </c>
+      <c r="G164" s="5" t="n">
+        <v>0.024892</v>
       </c>
       <c r="H164" s="5" t="n">
         <v>-0.319741</v>
@@ -17969,7 +17741,11 @@
           <t>Broker warrants issued in connection with the private placement (Note 8 (c)) $</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -18045,20 +17821,14 @@
           <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E171" s="5" t="n">
+        <v>-0.381999</v>
+      </c>
+      <c r="F171" s="5" t="n">
+        <v>-2.601251</v>
+      </c>
+      <c r="G171" s="5" t="n">
+        <v>-0.287774</v>
       </c>
       <c r="H171" s="5" t="n">
         <v>-0.033516</v>
@@ -18324,16 +18094,18 @@
           <t>Deferred income tax (recovery)</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F175" s="5" t="n">
+        <v>-0.64</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -18467,20 +18239,14 @@
           <t>OperatingCashFlow</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E177" s="5" t="n">
+        <v>-0.202764</v>
+      </c>
+      <c r="F177" s="5" t="n">
+        <v>-0.306212</v>
+      </c>
+      <c r="G177" s="5" t="n">
+        <v>-0.082152</v>
       </c>
       <c r="H177" s="5" t="n">
         <v>-1.458229</v>
@@ -18609,20 +18375,14 @@
           <t>InvestingCashFlow</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E179" s="5" t="n">
+        <v>0.023911</v>
+      </c>
+      <c r="F179" s="5" t="n">
+        <v>-0.1017</v>
+      </c>
+      <c r="G179" s="5" t="n">
+        <v>0.668254</v>
       </c>
       <c r="H179" s="5" t="n">
         <v>-0.017034</v>
@@ -18680,15 +18440,11 @@
           <t>CommonStockIssuance</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E180" s="5" t="n">
+        <v>0.249572</v>
+      </c>
+      <c r="F180" s="5" t="n">
+        <v>0.128125</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -18753,15 +18509,11 @@
           <t>FinancingCashFlow</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E181" s="5" t="n">
+        <v>0.235737</v>
+      </c>
+      <c r="F181" s="5" t="n">
+        <v>0.124035</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -19115,15 +18867,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F186" s="5" t="n">
+        <v>1.81741</v>
+      </c>
+      <c r="G186" s="5" t="n">
+        <v>0.172</v>
       </c>
       <c r="H186" s="5" t="n">
         <v>0.201</v>
@@ -19313,17 +19061,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments not affecting cash</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures (Note 8) $</t>
+          <t>Gain on disposition of mining interests</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -19337,15 +19085,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G189" s="5" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H189" s="5" t="n">
+        <v>-0.035</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -19372,27 +19116,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N189" s="5" t="n">
-        <v>6.222765</v>
-      </c>
-      <c r="O189" s="5" t="n">
-        <v>1.400094</v>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments not affecting cash</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Management fees and directors fees (Note 11)</t>
+          <t>Shareholder indemnification charges</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -19411,16 +19159,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I190" s="5" t="n">
-        <v>0.258999</v>
-      </c>
-      <c r="J190" s="5" t="n">
-        <v>0.253</v>
+      <c r="H190" s="5" t="n">
+        <v>-0.533913</v>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
@@ -19437,45 +19187,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N190" s="5" t="n">
-        <v>0.768099</v>
-      </c>
-      <c r="O190" s="5" t="n">
-        <v>1.121358</v>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Office, general and administrative</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E191" s="5" t="n">
-        <v>0.119986</v>
-      </c>
-      <c r="F191" s="5" t="n">
-        <v>0.112495</v>
+          <t>Proceeds on sale of capital assets</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G191" s="5" t="n">
-        <v>0.05464</v>
-      </c>
-      <c r="H191" s="5" t="n">
-        <v>0.06672500000000001</v>
+        <v>0.674</v>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -19487,36 +19243,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K191" s="5" t="n">
-        <v>0.682871</v>
-      </c>
-      <c r="L191" s="5" t="n">
-        <v>0.58418</v>
-      </c>
-      <c r="M191" s="5" t="n">
-        <v>0.711064</v>
-      </c>
-      <c r="N191" s="5" t="n">
-        <v>0.705637</v>
-      </c>
-      <c r="O191" s="5" t="n">
-        <v>0.401767</v>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Share-based payments (Note 7)</t>
+          <t>Proceeds on sale of mining interests</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -19530,15 +19296,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G192" s="5" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="H192" s="5" t="n">
+        <v>0.035</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -19565,153 +19327,177 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N192" s="5" t="n">
-        <v>0.112752</v>
-      </c>
-      <c r="O192" s="5" t="n">
-        <v>0.396948</v>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Professional and consulting fees</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Increase in mining interests</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" s="5" t="n">
+        <v>0.023911</v>
+      </c>
+      <c r="F193" s="5" t="n">
+        <v>-0.1959</v>
       </c>
       <c r="G193" s="5" t="n">
-        <v>0.018754</v>
+        <v>-0.031746</v>
       </c>
       <c r="H193" s="5" t="n">
-        <v>0.057382</v>
-      </c>
-      <c r="I193" s="5" t="n">
-        <v>0.350764</v>
-      </c>
-      <c r="J193" s="5" t="n">
-        <v>0.253597</v>
-      </c>
-      <c r="K193" s="5" t="n">
-        <v>0.296485</v>
-      </c>
-      <c r="L193" s="5" t="n">
-        <v>0.520353</v>
-      </c>
-      <c r="M193" s="5" t="n">
-        <v>0.604226</v>
-      </c>
-      <c r="N193" s="5" t="n">
-        <v>0.466452</v>
-      </c>
-      <c r="O193" s="5" t="n">
-        <v>0.168186</v>
+        <v>-0.052034</v>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments not affecting cash</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Public company costs</t>
+          <t>Gain on disposition of mining interest</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
-      <c r="E194" s="5" t="n">
-        <v>0.03727</v>
-      </c>
-      <c r="F194" s="5" t="n">
-        <v>0.024863</v>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G194" s="5" t="n">
-        <v>0.013347</v>
-      </c>
-      <c r="H194" s="5" t="n">
-        <v>0.04002</v>
-      </c>
-      <c r="I194" s="5" t="n">
-        <v>0.052789</v>
-      </c>
-      <c r="J194" s="5" t="n">
-        <v>0.060933</v>
-      </c>
-      <c r="K194" s="5" t="n">
-        <v>0.12984</v>
-      </c>
-      <c r="L194" s="5" t="n">
-        <v>0.175881</v>
-      </c>
-      <c r="M194" s="5" t="n">
-        <v>0.179259</v>
-      </c>
-      <c r="N194" s="5" t="n">
-        <v>0.143373</v>
-      </c>
-      <c r="O194" s="5" t="n">
-        <v>0.07985</v>
+        <v>-0.05</v>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments not affecting cash</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Flow through share premium</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F195" s="5" t="n">
+        <v>-0.0655</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -19748,27 +19534,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N195" s="5" t="n">
-        <v>0.8087490000000001</v>
-      </c>
-      <c r="O195" s="5" t="n">
-        <v>0.03421</v>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments not affecting cash</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Accretion (Notes 6 and 8)</t>
+          <t>Loss on disposal of marketable securities</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
@@ -19777,10 +19567,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F196" s="5" t="n">
+        <v>0.018035</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -19817,39 +19605,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N196" s="5" t="n">
-        <v>0.229271</v>
-      </c>
-      <c r="O196" s="5" t="n">
-        <v>0.020427</v>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Flow-through share premium recovery (Note 7)</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr"/>
+          <t>Proceeds on sale of marketable securities</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F197" s="5" t="n">
+        <v>0.09420000000000001</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -19886,39 +19680,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N197" s="5" t="n">
-        <v>-2.222778</v>
-      </c>
-      <c r="O197" s="5" t="n">
-        <v>-0.224756</v>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments not affecting cash</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Loss before the undernoted</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Deferred income taxes (recovery)</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
+      <c r="E198" s="5" t="n">
+        <v>0.09293999999999999</v>
+      </c>
+      <c r="F198" s="5" t="n">
+        <v>-0.64</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -19940,52 +19738,54 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K198" s="5" t="n">
-        <v>-3.848588</v>
-      </c>
-      <c r="L198" s="5" t="n">
-        <v>-8.238552</v>
-      </c>
-      <c r="M198" s="5" t="n">
-        <v>-10.56569</v>
-      </c>
-      <c r="N198" s="5" t="n">
-        <v>-7.23432</v>
-      </c>
-      <c r="O198" s="5" t="n">
-        <v>-3.398084</v>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Other income</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Change in cash and cash equivalents for the year</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" s="5" t="n">
+        <v>0.056884</v>
+      </c>
+      <c r="F199" s="5" t="n">
+        <v>-0.283877</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -19997,56 +19797,68 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I199" s="5" t="n">
-        <v>0.000943</v>
-      </c>
-      <c r="J199" s="5" t="n">
-        <v>0.011837</v>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L199" s="5" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="M199" s="5" t="n">
-        <v>0.238802</v>
-      </c>
-      <c r="N199" s="5" t="n">
-        <v>0.143899</v>
-      </c>
-      <c r="O199" s="5" t="n">
-        <v>0.083847</v>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Forgiveness of debt</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash and cash equivalents, beginning of year</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E200" s="5" t="n">
+        <v>0.26347</v>
+      </c>
+      <c r="F200" s="5" t="n">
+        <v>0.320354</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -20083,39 +19895,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N200" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O200" s="5" t="n">
-        <v>0.16</v>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Government grant (Note 8)</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr"/>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash and cash equivalents, end of year $</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E201" s="5" t="n">
+        <v>0.320354</v>
+      </c>
+      <c r="F201" s="5" t="n">
+        <v>0.036477</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -20152,11 +19968,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N201" s="5" t="n">
-        <v>0.0975</v>
-      </c>
-      <c r="O201" s="5" t="n">
-        <v>0.212</v>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="202">
@@ -20172,7 +19992,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Unrealized (loss) gain on marketable securities</t>
+          <t>Exploration and evaluation expenditures (Note 8) $</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -20211,17 +20031,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L202" s="5" t="n">
-        <v>0.049814</v>
-      </c>
-      <c r="M202" s="5" t="n">
-        <v>0.168397</v>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N202" s="5" t="n">
-        <v>0.230571</v>
+        <v>6.222765</v>
       </c>
       <c r="O202" s="5" t="n">
-        <v>-0.428076</v>
+        <v>1.400094</v>
       </c>
     </row>
     <row r="203">
@@ -20237,10 +20061,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Proceeds from property option agreement (Note 8)</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
+          <t>Management fees and directors fees (Note 11)</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -20261,15 +20089,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I203" s="5" t="n">
+        <v>0.258999</v>
+      </c>
+      <c r="J203" s="5" t="n">
+        <v>0.253</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
@@ -20287,10 +20111,10 @@
         </is>
       </c>
       <c r="N203" s="5" t="n">
-        <v>0.455</v>
+        <v>0.768099</v>
       </c>
       <c r="O203" s="5" t="n">
-        <v>0.4</v>
+        <v>1.121358</v>
       </c>
     </row>
     <row r="204">
@@ -20306,29 +20130,25 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Realized gain on marketable securities</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Office, general and administrative</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E204" s="5" t="n">
+        <v>0.119986</v>
+      </c>
+      <c r="F204" s="5" t="n">
+        <v>0.112495</v>
+      </c>
+      <c r="G204" s="5" t="n">
+        <v>0.05464</v>
+      </c>
+      <c r="H204" s="5" t="n">
+        <v>0.06672500000000001</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -20340,26 +20160,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K204" s="5" t="n">
+        <v>0.682871</v>
+      </c>
+      <c r="L204" s="5" t="n">
+        <v>0.58418</v>
+      </c>
+      <c r="M204" s="5" t="n">
+        <v>0.711064</v>
       </c>
       <c r="N204" s="5" t="n">
-        <v>0.554461</v>
+        <v>0.705637</v>
       </c>
       <c r="O204" s="5" t="n">
-        <v>0.695728</v>
+        <v>0.401767</v>
       </c>
     </row>
     <row r="205">
@@ -20375,7 +20189,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Impairment of right of use asset</t>
+          <t>Share-based payments (Note 7)</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -20425,12 +20239,10 @@
         </is>
       </c>
       <c r="N205" s="5" t="n">
-        <v>-0.303489</v>
-      </c>
-      <c r="O205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.112752</v>
+      </c>
+      <c r="O205" s="5" t="n">
+        <v>0.396948</v>
       </c>
     </row>
     <row r="206">
@@ -20446,12 +20258,12 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
+          <t>Professional and consulting fees</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -20464,46 +20276,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G206" s="5" t="n">
+        <v>0.018754</v>
+      </c>
+      <c r="H206" s="5" t="n">
+        <v>0.057382</v>
+      </c>
+      <c r="I206" s="5" t="n">
+        <v>0.350764</v>
+      </c>
+      <c r="J206" s="5" t="n">
+        <v>0.253597</v>
+      </c>
+      <c r="K206" s="5" t="n">
+        <v>0.296485</v>
+      </c>
+      <c r="L206" s="5" t="n">
+        <v>0.520353</v>
+      </c>
+      <c r="M206" s="5" t="n">
+        <v>0.604226</v>
       </c>
       <c r="N206" s="5" t="n">
-        <v>-6.036378</v>
+        <v>0.466452</v>
       </c>
       <c r="O206" s="5" t="n">
-        <v>-2.274585</v>
+        <v>0.168186</v>
       </c>
     </row>
     <row r="207">
@@ -20514,67 +20312,47 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Net loss per share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Public company costs</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" s="5" t="n">
+        <v>0.03727</v>
+      </c>
+      <c r="F207" s="5" t="n">
+        <v>0.024863</v>
+      </c>
+      <c r="G207" s="5" t="n">
+        <v>0.013347</v>
+      </c>
+      <c r="H207" s="5" t="n">
+        <v>0.04002</v>
+      </c>
+      <c r="I207" s="5" t="n">
+        <v>0.052789</v>
+      </c>
+      <c r="J207" s="5" t="n">
+        <v>0.060933</v>
+      </c>
+      <c r="K207" s="5" t="n">
+        <v>0.12984</v>
+      </c>
+      <c r="L207" s="5" t="n">
+        <v>0.175881</v>
       </c>
       <c r="M207" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>0.179259</v>
       </c>
       <c r="N207" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.143373</v>
       </c>
       <c r="O207" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.07985</v>
       </c>
     </row>
     <row r="208">
@@ -20585,17 +20363,17 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Net loss per share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -20644,10 +20422,10 @@
         </is>
       </c>
       <c r="N208" s="5" t="n">
-        <v>204.169109</v>
+        <v>0.8087490000000001</v>
       </c>
       <c r="O208" s="5" t="n">
-        <v>209.919142</v>
+        <v>0.03421</v>
       </c>
     </row>
     <row r="209">
@@ -20663,7 +20441,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures (Note 10) $</t>
+          <t>Accretion (Notes 6 and 8)</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -20702,19 +20480,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L209" s="5" t="n">
-        <v>7.339879</v>
-      </c>
-      <c r="M209" s="5" t="n">
-        <v>7.677737</v>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N209" s="5" t="n">
-        <v>6.222765</v>
-      </c>
-      <c r="O209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.229271</v>
+      </c>
+      <c r="O209" s="5" t="n">
+        <v>0.020427</v>
       </c>
     </row>
     <row r="210">
@@ -20730,7 +20510,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Management and directors fees (Note 15)</t>
+          <t>Flow-through share premium recovery (Note 7)</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -20774,16 +20554,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M210" s="5" t="n">
-        <v>1.100562</v>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N210" s="5" t="n">
-        <v>0.768099</v>
-      </c>
-      <c r="O210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.222778</v>
+      </c>
+      <c r="O210" s="5" t="n">
+        <v>-0.224756</v>
       </c>
     </row>
     <row r="211">
@@ -20799,7 +20579,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Share-based payments (Notes 9(b) and 15)</t>
+          <t>Loss before the undernoted</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -20833,26 +20613,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K211" s="5" t="n">
+        <v>-3.848588</v>
+      </c>
+      <c r="L211" s="5" t="n">
+        <v>-8.238552</v>
       </c>
       <c r="M211" s="5" t="n">
-        <v>0.770408</v>
+        <v>-10.56569</v>
       </c>
       <c r="N211" s="5" t="n">
-        <v>0.112752</v>
-      </c>
-      <c r="O211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-7.23432</v>
+      </c>
+      <c r="O211" s="5" t="n">
+        <v>-3.398084</v>
       </c>
     </row>
     <row r="212">
@@ -20868,12 +20642,12 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Professional and consulting fees (Note 15)</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -20896,36 +20670,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I212" s="5" t="n">
+        <v>0.000943</v>
+      </c>
+      <c r="J212" s="5" t="n">
+        <v>0.011837</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L212" s="5" t="n">
+        <v>0.027</v>
       </c>
       <c r="M212" s="5" t="n">
-        <v>0.604226</v>
+        <v>0.238802</v>
       </c>
       <c r="N212" s="5" t="n">
-        <v>0.466452</v>
-      </c>
-      <c r="O212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.143899</v>
+      </c>
+      <c r="O212" s="5" t="n">
+        <v>0.083847</v>
       </c>
     </row>
     <row r="213">
@@ -20941,14 +20707,10 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Amortization (Notes 7 and 8)</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Forgiveness of debt</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -20989,16 +20751,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M213" s="5" t="n">
-        <v>0.151197</v>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N213" s="5" t="n">
-        <v>0.8087490000000001</v>
-      </c>
-      <c r="O213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.02</v>
+      </c>
+      <c r="O213" s="5" t="n">
+        <v>0.16</v>
       </c>
     </row>
     <row r="214">
@@ -21014,7 +20776,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Accretion (Notes 8 and 10)</t>
+          <t>Government grant (Note 8)</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -21058,16 +20820,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M214" s="5" t="n">
-        <v>0.135237</v>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N214" s="5" t="n">
-        <v>0.229271</v>
-      </c>
-      <c r="O214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0975</v>
+      </c>
+      <c r="O214" s="5" t="n">
+        <v>0.212</v>
       </c>
     </row>
     <row r="215">
@@ -21083,7 +20845,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Flow-through share premium recovery (Note 9(d))</t>
+          <t>Unrealized (loss) gain on marketable securities</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -21122,21 +20884,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L215" s="5" t="n">
+        <v>0.049814</v>
       </c>
       <c r="M215" s="5" t="n">
-        <v>-0.764</v>
+        <v>0.168397</v>
       </c>
       <c r="N215" s="5" t="n">
-        <v>-2.222778</v>
-      </c>
-      <c r="O215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.230571</v>
+      </c>
+      <c r="O215" s="5" t="n">
+        <v>-0.428076</v>
       </c>
     </row>
     <row r="216">
@@ -21152,7 +20910,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Forgiveness of debt (Note 14)</t>
+          <t>Proceeds from property option agreement (Note 8)</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -21202,12 +20960,10 @@
         </is>
       </c>
       <c r="N216" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.455</v>
+      </c>
+      <c r="O216" s="5" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="217">
@@ -21223,7 +20979,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Government grant (Note 10)</t>
+          <t>Realized gain on marketable securities</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -21273,12 +21029,10 @@
         </is>
       </c>
       <c r="N217" s="5" t="n">
-        <v>0.0975</v>
-      </c>
-      <c r="O217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.554461</v>
+      </c>
+      <c r="O217" s="5" t="n">
+        <v>0.695728</v>
       </c>
     </row>
     <row r="218">
@@ -21294,7 +21048,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Unrealized gain on marketable securities (Note 5)</t>
+          <t>Impairment of right of use asset</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -21338,11 +21092,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M218" s="5" t="n">
-        <v>0.168397</v>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N218" s="5" t="n">
-        <v>0.230571</v>
+        <v>-0.303489</v>
       </c>
       <c r="O218" t="inlineStr">
         <is>
@@ -21363,10 +21119,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Proceeds from property option agreement (Notes 5 and 10)</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr"/>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -21407,16 +21167,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M219" s="5" t="n">
-        <v>0.13375</v>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N219" s="5" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="O219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.036378</v>
+      </c>
+      <c r="O219" s="5" t="n">
+        <v>-2.274585</v>
       </c>
     </row>
     <row r="220">
@@ -21427,15 +21187,19 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net loss per share</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Realized (loss) gain on marketable securities (Note 5)</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr"/>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -21477,15 +21241,13 @@
         </is>
       </c>
       <c r="M220" s="5" t="n">
-        <v>-0.347021</v>
+        <v>-5.999999999999999e-08</v>
       </c>
       <c r="N220" s="5" t="n">
-        <v>0.554461</v>
-      </c>
-      <c r="O220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3e-08</v>
+      </c>
+      <c r="O220" s="5" t="n">
+        <v>-1e-08</v>
       </c>
     </row>
     <row r="221">
@@ -21496,15 +21258,19 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net loss per share</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Impairment loss on right of use asset (Note 8)</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -21551,12 +21317,10 @@
         </is>
       </c>
       <c r="N221" s="5" t="n">
-        <v>-0.303489</v>
-      </c>
-      <c r="O221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>204.169109</v>
+      </c>
+      <c r="O221" s="5" t="n">
+        <v>209.919142</v>
       </c>
     </row>
     <row r="222">
@@ -21572,14 +21336,10 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation expenditures (Note 10) $</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -21615,16 +21375,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L222" s="5" t="n">
+        <v>7.339879</v>
       </c>
       <c r="M222" s="5" t="n">
-        <v>-10.371762</v>
+        <v>7.677737</v>
       </c>
       <c r="N222" s="5" t="n">
-        <v>-6.036378</v>
+        <v>6.222765</v>
       </c>
       <c r="O222" t="inlineStr">
         <is>
@@ -21640,17 +21398,17 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Net loss per share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic</t>
+          <t>Management and directors fees (Note 15)</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -21694,10 +21452,10 @@
         </is>
       </c>
       <c r="M223" s="5" t="n">
-        <v>170.024203</v>
+        <v>1.100562</v>
       </c>
       <c r="N223" s="5" t="n">
-        <v>204.169109</v>
+        <v>0.768099</v>
       </c>
       <c r="O223" t="inlineStr">
         <is>
@@ -21718,7 +21476,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Management fees and directors fees (Note 15)</t>
+          <t>Share-based payments (Notes 9(b) and 15)</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
@@ -21757,16 +21515,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L224" s="5" t="n">
-        <v>0.246322</v>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M224" s="5" t="n">
-        <v>1.100562</v>
-      </c>
-      <c r="N224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.770408</v>
+      </c>
+      <c r="N224" s="5" t="n">
+        <v>0.112752</v>
       </c>
       <c r="O224" t="inlineStr">
         <is>
@@ -21787,10 +21545,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Share-based payments (Note 9(b) and 15)</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr"/>
+          <t>Professional and consulting fees (Note 15)</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -21826,16 +21588,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L225" s="5" t="n">
-        <v>0.549779</v>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M225" s="5" t="n">
-        <v>0.770408</v>
-      </c>
-      <c r="N225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.604226</v>
+      </c>
+      <c r="N225" s="5" t="n">
+        <v>0.466452</v>
       </c>
       <c r="O225" t="inlineStr">
         <is>
@@ -21856,7 +21618,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Amortization (Note 7 and 8)</t>
+          <t>Amortization (Notes 7 and 8)</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -21899,16 +21661,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L226" s="5" t="n">
-        <v>0.025248</v>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M226" s="5" t="n">
         <v>0.151197</v>
       </c>
-      <c r="N226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N226" s="5" t="n">
+        <v>0.8087490000000001</v>
       </c>
       <c r="O226" t="inlineStr">
         <is>
@@ -21929,7 +21691,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Flow-through share premium recovery (Note 9(a))</t>
+          <t>Accretion (Notes 8 and 10)</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -21968,16 +21730,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L227" s="5" t="n">
-        <v>-1.20309</v>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M227" s="5" t="n">
-        <v>-0.764</v>
-      </c>
-      <c r="N227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.135237</v>
+      </c>
+      <c r="N227" s="5" t="n">
+        <v>0.229271</v>
       </c>
       <c r="O227" t="inlineStr">
         <is>
@@ -21998,7 +21760,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Gain on disposition of exploration and evaluation properties (Notes 5 and 10)</t>
+          <t>Flow-through share premium recovery (Note 9(d))</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
@@ -22037,16 +21799,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L228" s="5" t="n">
-        <v>8.697749999999999</v>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M228" s="5" t="n">
-        <v>0.13375</v>
-      </c>
-      <c r="N228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.764</v>
+      </c>
+      <c r="N228" s="5" t="n">
+        <v>-2.222778</v>
       </c>
       <c r="O228" t="inlineStr">
         <is>
@@ -22067,7 +21829,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Realized (loss) on marketable securities</t>
+          <t>Forgiveness of debt (Note 14)</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
@@ -22106,16 +21868,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L229" s="5" t="n">
-        <v>-0.260256</v>
-      </c>
-      <c r="M229" s="5" t="n">
-        <v>-0.347021</v>
-      </c>
-      <c r="N229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N229" s="5" t="n">
+        <v>0.02</v>
       </c>
       <c r="O229" t="inlineStr">
         <is>
@@ -22136,14 +21900,10 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Net income (loss) and comprehensive income (loss) for the year $</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Government grant (Note 10)</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -22174,19 +21934,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K230" s="5" t="n">
-        <v>-3.852669</v>
-      </c>
-      <c r="L230" s="5" t="n">
-        <v>0.275756</v>
-      </c>
-      <c r="M230" s="5" t="n">
-        <v>-10.371762</v>
-      </c>
-      <c r="N230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N230" s="5" t="n">
+        <v>0.0975</v>
       </c>
       <c r="O230" t="inlineStr">
         <is>
@@ -22202,12 +21966,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Net income (loss) per share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Basic and diluted earnings (loss) per share $</t>
+          <t>Unrealized gain on marketable securities (Note 5)</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
@@ -22246,16 +22010,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L231" s="5" t="n">
-        <v>0</v>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M231" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
-      </c>
-      <c r="N231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.168397</v>
+      </c>
+      <c r="N231" s="5" t="n">
+        <v>0.230571</v>
       </c>
       <c r="O231" t="inlineStr">
         <is>
@@ -22271,19 +22035,15 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Net income (loss) per share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding - basic</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Proceeds from property option agreement (Notes 5 and 10)</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -22314,19 +22074,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K232" s="5" t="n">
-        <v>87.646078</v>
-      </c>
-      <c r="L232" s="5" t="n">
-        <v>124.56683</v>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M232" s="5" t="n">
-        <v>170.024203</v>
-      </c>
-      <c r="N232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.13375</v>
+      </c>
+      <c r="N232" s="5" t="n">
+        <v>0.455</v>
       </c>
       <c r="O232" t="inlineStr">
         <is>
@@ -22347,7 +22109,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures (Note 9) $</t>
+          <t>Realized (loss) gain on marketable securities (Note 5)</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -22381,21 +22143,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K233" s="5" t="n">
-        <v>2.398422</v>
-      </c>
-      <c r="L233" s="5" t="n">
-        <v>7.339879</v>
-      </c>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M233" s="5" t="n">
+        <v>-0.347021</v>
+      </c>
+      <c r="N233" s="5" t="n">
+        <v>0.554461</v>
       </c>
       <c r="O233" t="inlineStr">
         <is>
@@ -22416,7 +22178,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Management fees and directors fees (Note 14)</t>
+          <t>Impairment loss on right of use asset (Note 8)</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -22450,21 +22212,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K234" s="5" t="n">
-        <v>0.3205</v>
-      </c>
-      <c r="L234" s="5" t="n">
-        <v>0.246322</v>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N234" s="5" t="n">
+        <v>-0.303489</v>
       </c>
       <c r="O234" t="inlineStr">
         <is>
@@ -22485,10 +22249,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Share-based payments (Note 8(b))</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -22519,21 +22287,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K235" s="5" t="n">
-        <v>0.52784</v>
-      </c>
-      <c r="L235" s="5" t="n">
-        <v>0.549779</v>
-      </c>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M235" s="5" t="n">
+        <v>-10.371762</v>
+      </c>
+      <c r="N235" s="5" t="n">
+        <v>-6.036378</v>
       </c>
       <c r="O235" t="inlineStr">
         <is>
@@ -22549,17 +22317,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net loss per share</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Amortization (Note 7)</t>
+          <t>Weighted average number of common shares outstanding – basic</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -22567,14 +22335,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F236" s="5" t="n">
-        <v>0.001254</v>
-      </c>
-      <c r="G236" s="5" t="n">
-        <v>0.000833</v>
-      </c>
-      <c r="H236" s="5" t="n">
-        <v>0.0007</v>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
@@ -22586,21 +22360,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K236" s="5" t="n">
-        <v>0.012391</v>
-      </c>
-      <c r="L236" s="5" t="n">
-        <v>0.025248</v>
-      </c>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M236" s="5" t="n">
+        <v>170.024203</v>
+      </c>
+      <c r="N236" s="5" t="n">
+        <v>204.169109</v>
       </c>
       <c r="O236" t="inlineStr">
         <is>
@@ -22621,10 +22395,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Flow-through share premium recovery (Note 8(a))</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>Management fees and directors fees (Note 15)</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -22655,16 +22433,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K237" s="5" t="n">
-        <v>-0.519761</v>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L237" s="5" t="n">
-        <v>-1.20309</v>
-      </c>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.246322</v>
+      </c>
+      <c r="M237" s="5" t="n">
+        <v>1.100562</v>
       </c>
       <c r="N237" t="inlineStr">
         <is>
@@ -22690,14 +22468,10 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Share-based payments (Note 9(b) and 15)</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -22734,12 +22508,10 @@
         </is>
       </c>
       <c r="L238" s="5" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="M238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.549779</v>
+      </c>
+      <c r="M238" s="5" t="n">
+        <v>0.770408</v>
       </c>
       <c r="N238" t="inlineStr">
         <is>
@@ -22765,10 +22537,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Unrealized gain on marketable securities</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
+          <t>Amortization (Note 7 and 8)</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -22799,16 +22575,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K239" s="5" t="n">
-        <v>-0.004081</v>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L239" s="5" t="n">
-        <v>0.049814</v>
-      </c>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.025248</v>
+      </c>
+      <c r="M239" s="5" t="n">
+        <v>0.151197</v>
       </c>
       <c r="N239" t="inlineStr">
         <is>
@@ -22834,7 +22610,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Realized loss on marketable securities</t>
+          <t>Flow-through share premium recovery (Note 9(a))</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -22874,12 +22650,10 @@
         </is>
       </c>
       <c r="L240" s="5" t="n">
-        <v>-0.260256</v>
-      </c>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.20309</v>
+      </c>
+      <c r="M240" s="5" t="n">
+        <v>-0.764</v>
       </c>
       <c r="N240" t="inlineStr">
         <is>
@@ -22905,7 +22679,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Gain on disposition of exploration and evaluation properties (Note 9)</t>
+          <t>Gain on disposition of exploration and evaluation properties (Notes 5 and 10)</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -22947,10 +22721,8 @@
       <c r="L241" s="5" t="n">
         <v>8.697749999999999</v>
       </c>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M241" s="5" t="n">
+        <v>0.13375</v>
       </c>
       <c r="N241" t="inlineStr">
         <is>
@@ -22971,19 +22743,15 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Net income (loss) per share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Basic earnings (loss) per share $</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Realized (loss) on marketable securities</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -23014,16 +22782,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K242" s="5" t="n">
-        <v>-4e-08</v>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L242" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.260256</v>
+      </c>
+      <c r="M242" s="5" t="n">
+        <v>-0.347021</v>
       </c>
       <c r="N242" t="inlineStr">
         <is>
@@ -23044,17 +22812,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Net income (loss) per share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Diluted earnings (loss) per share $</t>
+          <t>Net income (loss) and comprehensive income (loss) for the year $</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>DilutedEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -23087,18 +22855,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K243" s="5" t="n">
+        <v>-3.852669</v>
       </c>
       <c r="L243" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.275756</v>
+      </c>
+      <c r="M243" s="5" t="n">
+        <v>-10.371762</v>
       </c>
       <c r="N243" t="inlineStr">
         <is>
@@ -23124,14 +22888,10 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding - diluted</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>DilutedAverageShares</t>
-        </is>
-      </c>
+          <t>Basic and diluted earnings (loss) per share $</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -23168,12 +22928,10 @@
         </is>
       </c>
       <c r="L244" s="5" t="n">
-        <v>124.91683</v>
-      </c>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="M244" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
       </c>
       <c r="N244" t="inlineStr">
         <is>
@@ -23194,17 +22952,17 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net income (loss) per share</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Office, general and administrative $</t>
+          <t>Weighted average number of common shares outstanding - basic</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -23222,29 +22980,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H245" s="5" t="n">
-        <v>0.06672500000000001</v>
-      </c>
-      <c r="I245" s="5" t="n">
-        <v>0.279689</v>
-      </c>
-      <c r="J245" s="5" t="n">
-        <v>0.14625</v>
-      </c>
-      <c r="K245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K245" s="5" t="n">
+        <v>87.646078</v>
+      </c>
+      <c r="L245" s="5" t="n">
+        <v>124.56683</v>
+      </c>
+      <c r="M245" s="5" t="n">
+        <v>170.024203</v>
       </c>
       <c r="N245" t="inlineStr">
         <is>
@@ -23270,7 +23028,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Share-based payments, (Note 8(b))</t>
+          <t>Exploration and evaluation expenditures (Note 9) $</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
@@ -23299,18 +23057,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J246" s="5" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L246" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K246" s="5" t="n">
+        <v>2.398422</v>
+      </c>
+      <c r="L246" s="5" t="n">
+        <v>7.339879</v>
       </c>
       <c r="M246" t="inlineStr">
         <is>
@@ -23341,43 +23097,49 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Amortization, (Note 7)</t>
+          <t>Management fees and directors fees (Note 14)</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E247" s="5" t="n">
-        <v>0.00172</v>
-      </c>
-      <c r="F247" s="5" t="n">
-        <v>0.001254</v>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H247" s="5" t="n">
-        <v>0.0007</v>
-      </c>
-      <c r="I247" s="5" t="n">
-        <v>0.000516</v>
-      </c>
-      <c r="J247" s="5" t="n">
-        <v>0.012688</v>
-      </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L247" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K247" s="5" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="L247" s="5" t="n">
+        <v>0.246322</v>
       </c>
       <c r="M247" t="inlineStr">
         <is>
@@ -23408,7 +23170,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Due diligence costs, (Note 6)</t>
+          <t>Share-based payments (Note 8(b))</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
@@ -23432,23 +23194,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I248" s="5" t="n">
-        <v>0.307612</v>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K248" s="5" t="n">
+        <v>0.52784</v>
+      </c>
+      <c r="L248" s="5" t="n">
+        <v>0.549779</v>
       </c>
       <c r="M248" t="inlineStr">
         <is>
@@ -23479,37 +23239,43 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Loss from operations before the undernoted</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr"/>
-      <c r="E249" s="5" t="n">
-        <v>-0.32956</v>
+          <t>Amortization (Note 7)</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F249" s="5" t="n">
-        <v>-0.230504</v>
+        <v>0.001254</v>
       </c>
       <c r="G249" s="5" t="n">
-        <v>-0.115774</v>
+        <v>0.000833</v>
       </c>
       <c r="H249" s="5" t="n">
-        <v>-0.829429</v>
-      </c>
-      <c r="I249" s="5" t="n">
-        <v>-1.250369</v>
-      </c>
-      <c r="J249" s="5" t="n">
-        <v>-0.771468</v>
-      </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0007</v>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K249" s="5" t="n">
+        <v>0.012391</v>
+      </c>
+      <c r="L249" s="5" t="n">
+        <v>0.025248</v>
       </c>
       <c r="M249" t="inlineStr">
         <is>
@@ -23540,7 +23306,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Shareholder indemnification recovery, (Note 9)</t>
+          <t>Flow-through share premium recovery (Note 8(a))</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
@@ -23559,24 +23325,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H250" s="5" t="n">
-        <v>0.533913</v>
-      </c>
-      <c r="I250" s="5" t="n">
-        <v>0.165899</v>
-      </c>
-      <c r="J250" s="5" t="n">
-        <v>0.09996099999999999</v>
-      </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K250" s="5" t="n">
+        <v>-0.519761</v>
+      </c>
+      <c r="L250" s="5" t="n">
+        <v>-1.20309</v>
       </c>
       <c r="M250" t="inlineStr">
         <is>
@@ -23607,41 +23375,51 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Net loss before provision for income taxes</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
-      <c r="E251" s="5" t="n">
-        <v>-0.289059</v>
-      </c>
-      <c r="F251" s="5" t="n">
-        <v>-3.241251</v>
-      </c>
-      <c r="G251" s="5" t="n">
-        <v>-0.287774</v>
-      </c>
-      <c r="H251" s="5" t="n">
-        <v>-0.496516</v>
-      </c>
-      <c r="I251" s="5" t="n">
-        <v>-1.083527</v>
-      </c>
-      <c r="J251" s="5" t="n">
-        <v>-0.65967</v>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L251" s="5" t="n">
+        <v>0.027</v>
       </c>
       <c r="M251" t="inlineStr">
         <is>
@@ -23672,7 +23450,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery, (Note 12(a))</t>
+          <t>Unrealized gain on marketable securities</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
@@ -23696,23 +23474,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I252" s="5" t="n">
-        <v>0.043</v>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K252" s="5" t="n">
+        <v>-0.004081</v>
+      </c>
+      <c r="L252" s="5" t="n">
+        <v>0.049814</v>
       </c>
       <c r="M252" t="inlineStr">
         <is>
@@ -23743,14 +23519,10 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Realized loss on marketable securities</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -23771,21 +23543,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I253" s="5" t="n">
-        <v>-1.040527</v>
-      </c>
-      <c r="J253" s="5" t="n">
-        <v>-0.65967</v>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L253" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L253" s="5" t="n">
+        <v>-0.260256</v>
       </c>
       <c r="M253" t="inlineStr">
         <is>
@@ -23811,19 +23585,15 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Gain on disposition of exploration and evaluation properties (Note 9)</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -23834,27 +23604,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G254" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="H254" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I254" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="J254" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L254" s="5" t="n">
+        <v>8.697749999999999</v>
       </c>
       <c r="M254" t="inlineStr">
         <is>
@@ -23880,15 +23656,19 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding -</t>
+          <t>Net income (loss) per share</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding - basic and diluted</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
+          <t>Basic earnings (loss) per share $</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -23899,27 +23679,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G255" s="5" t="n">
-        <v>25.64726</v>
-      </c>
-      <c r="H255" s="5" t="n">
-        <v>27.785261</v>
-      </c>
-      <c r="I255" s="5" t="n">
-        <v>42.178143</v>
-      </c>
-      <c r="J255" s="5" t="n">
-        <v>42.660336</v>
-      </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K255" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="L255" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="M255" t="inlineStr">
         <is>
@@ -23945,29 +23729,43 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net income (loss) per share</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Management fees and directors fees</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr"/>
-      <c r="E256" s="5" t="n">
-        <v>0.139678</v>
-      </c>
-      <c r="F256" s="5" t="n">
-        <v>0.07375</v>
-      </c>
-      <c r="G256" s="5" t="n">
-        <v>0.07820000000000001</v>
-      </c>
-      <c r="H256" s="5" t="n">
-        <v>0.165167</v>
-      </c>
-      <c r="I256" s="5" t="n">
-        <v>0.258999</v>
+          <t>Diluted earnings (loss) per share $</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
@@ -23979,10 +23777,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L256" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="M256" t="inlineStr">
         <is>
@@ -24008,15 +23804,19 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net income (loss) per share</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Stock based compensation, (Note 8(b))</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding - diluted</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -24032,8 +23832,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H257" s="5" t="n">
-        <v>0.534435</v>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
@@ -24050,10 +23852,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L257" s="5" t="n">
+        <v>124.91683</v>
       </c>
       <c r="M257" t="inlineStr">
         <is>
@@ -24084,12 +23884,12 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Professional and consulting fees, (Note 10)</t>
+          <t>Office, general and administrative $</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -24108,15 +23908,13 @@
         </is>
       </c>
       <c r="H258" s="5" t="n">
-        <v>0.057382</v>
+        <v>0.06672500000000001</v>
       </c>
       <c r="I258" s="5" t="n">
-        <v>0.350764</v>
-      </c>
-      <c r="J258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.279689</v>
+      </c>
+      <c r="J258" s="5" t="n">
+        <v>0.14625</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
@@ -24157,7 +23955,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Gain on disposition of exploration and evaluation assets, (Note 6)</t>
+          <t>Share-based payments, (Note 8(b))</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -24176,18 +23974,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H259" s="5" t="n">
-        <v>-0.035</v>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J259" s="5" t="n">
+        <v>0.045</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
@@ -24228,37 +24026,33 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Due diligence fees, (Note 6)</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr"/>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Amortization, (Note 7)</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E260" s="5" t="n">
+        <v>0.00172</v>
+      </c>
+      <c r="F260" s="5" t="n">
+        <v>0.001254</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H260" s="5" t="n">
+        <v>0.0007</v>
       </c>
       <c r="I260" s="5" t="n">
-        <v>0.307612</v>
-      </c>
-      <c r="J260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000516</v>
+      </c>
+      <c r="J260" s="5" t="n">
+        <v>0.012688</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
@@ -24299,14 +24093,10 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Impairment of capital assets, (Note 7)</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>ImpairmentOfCapitalAssets</t>
-        </is>
-      </c>
+          <t>Due diligence costs, (Note 6)</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -24322,13 +24112,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H261" s="5" t="n">
-        <v>-0.201</v>
-      </c>
-      <c r="I261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I261" s="5" t="n">
+        <v>0.307612</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
@@ -24374,33 +24164,27 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery, (Note 11(a))</t>
+          <t>Loss from operations before the undernoted</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E262" s="5" t="n">
+        <v>-0.32956</v>
       </c>
       <c r="F262" s="5" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.230504</v>
+      </c>
+      <c r="G262" s="5" t="n">
+        <v>-0.115774</v>
       </c>
       <c r="H262" s="5" t="n">
-        <v>0.463</v>
+        <v>-0.829429</v>
       </c>
       <c r="I262" s="5" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="J262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.250369</v>
+      </c>
+      <c r="J262" s="5" t="n">
+        <v>-0.771468</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
@@ -24441,33 +24225,33 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E263" s="5" t="n">
-        <v>-0.381999</v>
-      </c>
-      <c r="F263" s="5" t="n">
-        <v>-2.601251</v>
-      </c>
-      <c r="G263" s="5" t="n">
-        <v>-0.287774</v>
+          <t>Shareholder indemnification recovery, (Note 9)</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H263" s="5" t="n">
-        <v>-0.033516</v>
+        <v>0.533913</v>
       </c>
       <c r="I263" s="5" t="n">
-        <v>-1.040527</v>
-      </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.165899</v>
+      </c>
+      <c r="J263" s="5" t="n">
+        <v>0.09996099999999999</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
@@ -24503,42 +24287,36 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Net (decrease) increase in fair value of marketable securities</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr"/>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss before provision for income taxes</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E264" s="5" t="n">
+        <v>-0.289059</v>
+      </c>
+      <c r="F264" s="5" t="n">
+        <v>-3.241251</v>
+      </c>
+      <c r="G264" s="5" t="n">
+        <v>-0.287774</v>
       </c>
       <c r="H264" s="5" t="n">
-        <v>0.013147</v>
-      </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.496516</v>
+      </c>
+      <c r="I264" s="5" t="n">
+        <v>-1.083527</v>
+      </c>
+      <c r="J264" s="5" t="n">
+        <v>-0.65967</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
@@ -24574,17 +24352,17 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year $</t>
+          <t>Deferred income tax recovery, (Note 12(a))</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -24602,11 +24380,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H265" s="5" t="n">
-        <v>-0.020369</v>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I265" s="5" t="n">
-        <v>-1.040527</v>
+        <v>0.043</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -24647,17 +24427,17 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding - basic and diluted</t>
+          <t>Net loss and comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -24665,22 +24445,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F266" s="5" t="n">
-        <v>255.985803</v>
-      </c>
-      <c r="G266" s="5" t="n">
-        <v>256.475301</v>
-      </c>
-      <c r="H266" s="5" t="n">
-        <v>27.785261</v>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I266" s="5" t="n">
-        <v>42.178143</v>
-      </c>
-      <c r="J266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.040527</v>
+      </c>
+      <c r="J266" s="5" t="n">
+        <v>-0.65967</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
@@ -24716,15 +24500,19 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Gain on disposition of mining interests (Note 6)</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr"/>
+          <t>Basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -24736,20 +24524,16 @@
         </is>
       </c>
       <c r="G267" s="5" t="n">
-        <v>-0.05</v>
+        <v>-1e-08</v>
       </c>
       <c r="H267" s="5" t="n">
-        <v>-0.035</v>
-      </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="I267" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="J267" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
@@ -24785,42 +24569,36 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common shares outstanding -</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Impairment of capital assets (Note 7)</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>ImpairmentOfCapitalAssets</t>
-        </is>
-      </c>
+          <t>Weighted average number of common shares outstanding - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F268" s="5" t="n">
-        <v>-1.81741</v>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G268" s="5" t="n">
-        <v>-0.172</v>
+        <v>25.64726</v>
       </c>
       <c r="H268" s="5" t="n">
-        <v>-0.201</v>
-      </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>27.785261</v>
+      </c>
+      <c r="I268" s="5" t="n">
+        <v>42.178143</v>
+      </c>
+      <c r="J268" s="5" t="n">
+        <v>42.660336</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
@@ -24861,32 +24639,28 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Shareholder indemnification recovery, (Note 9(b))</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Management fees and directors fees</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E269" s="5" t="n">
+        <v>0.139678</v>
+      </c>
+      <c r="F269" s="5" t="n">
+        <v>0.07375</v>
+      </c>
+      <c r="G269" s="5" t="n">
+        <v>0.07820000000000001</v>
       </c>
       <c r="H269" s="5" t="n">
-        <v>0.533913</v>
-      </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.165167</v>
+      </c>
+      <c r="I269" s="5" t="n">
+        <v>0.258999</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
@@ -24927,12 +24701,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Net increase (decrease) in fair value of marketable</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Net increase (decrease) in fair value of marketable securities</t>
+          <t>Stock based compensation, (Note 8(b))</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -24946,11 +24720,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G270" s="5" t="n">
-        <v>-0.003604</v>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H270" s="5" t="n">
-        <v>0.013147</v>
+        <v>0.534435</v>
       </c>
       <c r="I270" t="inlineStr">
         <is>
@@ -24996,17 +24772,17 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Net increase (decrease) in fair value of marketable</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year $</t>
+          <t>Professional and consulting fees, (Note 10)</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -25019,16 +24795,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G271" s="5" t="n">
-        <v>-0.291378</v>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H271" s="5" t="n">
-        <v>-0.020369</v>
-      </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.057382</v>
+      </c>
+      <c r="I271" s="5" t="n">
+        <v>0.350764</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
@@ -25074,7 +24850,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Management fees and directors fees (Note 10)</t>
+          <t>Gain on disposition of exploration and evaluation assets, (Note 6)</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
@@ -25083,16 +24859,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F272" s="5" t="n">
-        <v>0.07375</v>
-      </c>
-      <c r="G272" s="5" t="n">
-        <v>0.07820000000000001</v>
-      </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H272" s="5" t="n">
+        <v>-0.035</v>
       </c>
       <c r="I272" t="inlineStr">
         <is>
@@ -25143,34 +24921,32 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Professional fees (Note 10)</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Due diligence fees, (Note 6)</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F273" s="5" t="n">
-        <v>0.018142</v>
-      </c>
-      <c r="G273" s="5" t="n">
-        <v>0.018754</v>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I273" s="5" t="n">
+        <v>0.307612</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
@@ -25216,10 +24992,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Gain on disposition of mining interests</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr"/>
+          <t>Impairment of capital assets, (Note 7)</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>ImpairmentOfCapitalAssets</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -25230,13 +25010,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G274" s="5" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H274" s="5" t="n">
+        <v>-0.201</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
@@ -25287,32 +25067,32 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Flow-through share premium income</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr"/>
+          <t>Deferred income tax recovery, (Note 11(a))</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F275" s="5" t="n">
-        <v>0.0655</v>
+        <v>0.64</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H275" s="5" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="I275" s="5" t="n">
+        <v>0.043</v>
       </c>
       <c r="J275" t="inlineStr">
         <is>
@@ -25358,32 +25138,28 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Shareholder indemnification charges, (Note 9)</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr"/>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E276" s="5" t="n">
+        <v>-0.381999</v>
       </c>
       <c r="F276" s="5" t="n">
-        <v>-1.241</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.601251</v>
+      </c>
+      <c r="G276" s="5" t="n">
+        <v>-0.287774</v>
+      </c>
+      <c r="H276" s="5" t="n">
+        <v>-0.033516</v>
+      </c>
+      <c r="I276" s="5" t="n">
+        <v>-1.040527</v>
       </c>
       <c r="J276" t="inlineStr">
         <is>
@@ -25424,12 +25200,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Other loss</t>
+          <t>Net (decrease) increase in fair value of marketable securities</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
@@ -25438,18 +25214,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F277" s="5" t="n">
-        <v>-0.017837</v>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H277" s="5" t="n">
+        <v>0.013147</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
@@ -25495,33 +25271,39 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Net increase (decrease) in fair value of marketable securities</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr"/>
-      <c r="E278" s="5" t="n">
-        <v>-0.025632</v>
-      </c>
-      <c r="F278" s="5" t="n">
-        <v>0.066454</v>
-      </c>
-      <c r="G278" s="5" t="n">
-        <v>-0.003604</v>
-      </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H278" s="5" t="n">
+        <v>-0.020369</v>
+      </c>
+      <c r="I278" s="5" t="n">
+        <v>-1.040527</v>
       </c>
       <c r="J278" t="inlineStr">
         <is>
@@ -25562,37 +25344,35 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year $</t>
+          <t>Weighted average number of common shares outstanding - basic and diluted</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E279" s="5" t="n">
-        <v>-0.407631</v>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F279" s="5" t="n">
-        <v>-2.534797</v>
+        <v>255.985803</v>
       </c>
       <c r="G279" s="5" t="n">
-        <v>-0.291378</v>
-      </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>256.475301</v>
+      </c>
+      <c r="H279" s="5" t="n">
+        <v>27.785261</v>
+      </c>
+      <c r="I279" s="5" t="n">
+        <v>42.178143</v>
       </c>
       <c r="J279" t="inlineStr">
         <is>
@@ -25633,34 +25413,30 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Gain on disposition of mining interests (Note 6)</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F280" s="5" t="n">
-        <v>-1e-08</v>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G280" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.05</v>
+      </c>
+      <c r="H280" s="5" t="n">
+        <v>-0.035</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
@@ -25711,29 +25487,27 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Impairment of capital assets (Note 7)</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E281" s="5" t="n">
-        <v>0.030906</v>
+          <t>ImpairmentOfCapitalAssets</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F281" s="5" t="n">
-        <v>0.018142</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.81741</v>
+      </c>
+      <c r="G281" s="5" t="n">
+        <v>-0.172</v>
+      </c>
+      <c r="H281" s="5" t="n">
+        <v>-0.201</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
@@ -25784,25 +25558,27 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Other income (loss)</t>
+          <t>Shareholder indemnification recovery, (Note 9(b))</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
-      <c r="E282" s="5" t="n">
-        <v>0.040501</v>
-      </c>
-      <c r="F282" s="5" t="n">
-        <v>-0.017837</v>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H282" s="5" t="n">
+        <v>0.533913</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
@@ -25848,30 +25624,30 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net increase (decrease) in fair value of marketable</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery (expense), (Note 11(a))</t>
+          <t>Net increase (decrease) in fair value of marketable securities</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
-      <c r="E283" s="5" t="n">
-        <v>-0.09293999999999999</v>
-      </c>
-      <c r="F283" s="5" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G283" s="5" t="n">
+        <v>-0.003604</v>
+      </c>
+      <c r="H283" s="5" t="n">
+        <v>0.013147</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
@@ -25917,30 +25693,34 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Basic and diluted                                                                    $(0.01)            $0.00</t>
+          <t>Net increase (decrease) in fair value of marketable</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding - basic and diluted</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr"/>
-      <c r="E284" s="5" t="n">
-        <v>230.128052</v>
-      </c>
-      <c r="F284" s="5" t="n">
-        <v>255.985803</v>
-      </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G284" s="5" t="n">
+        <v>-0.291378</v>
+      </c>
+      <c r="H284" s="5" t="n">
+        <v>-0.020369</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
@@ -25986,27 +25766,29 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Basic and diluted                                                                    $(0.01)            $0.00</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Basic and diluted                                                                    $(0.01)            $0.00 total</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr"/>
-      <c r="E285" s="5" t="n">
-        <v>0.066454</v>
-      </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Management fees and directors fees (Note 10)</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F285" s="5" t="n">
+        <v>0.07375</v>
+      </c>
+      <c r="G285" s="5" t="n">
+        <v>0.07820000000000001</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -26057,64 +25839,987 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Professional fees (Note 10)</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F286" s="5" t="n">
+        <v>0.018142</v>
+      </c>
+      <c r="G286" s="5" t="n">
+        <v>0.018754</v>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Gain on disposition of mining interests</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G287" s="5" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Flow-through share premium income</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr"/>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F288" s="5" t="n">
+        <v>0.0655</v>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Shareholder indemnification charges, (Note 9)</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F289" s="5" t="n">
+        <v>-1.241</v>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Other loss</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F290" s="5" t="n">
+        <v>-0.017837</v>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Net increase (decrease) in fair value of marketable securities</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" s="5" t="n">
+        <v>-0.025632</v>
+      </c>
+      <c r="F291" s="5" t="n">
+        <v>0.066454</v>
+      </c>
+      <c r="G291" s="5" t="n">
+        <v>-0.003604</v>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E292" s="5" t="n">
+        <v>-0.407631</v>
+      </c>
+      <c r="F292" s="5" t="n">
+        <v>-2.534797</v>
+      </c>
+      <c r="G292" s="5" t="n">
+        <v>-0.291378</v>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Loss per share</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F293" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="G293" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E294" s="5" t="n">
+        <v>0.030906</v>
+      </c>
+      <c r="F294" s="5" t="n">
+        <v>0.018142</v>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Other income (loss)</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" s="5" t="n">
+        <v>0.040501</v>
+      </c>
+      <c r="F295" s="5" t="n">
+        <v>-0.017837</v>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Deferred income tax recovery (expense), (Note 11(a))</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E296" s="5" t="n">
+        <v>-0.09293999999999999</v>
+      </c>
+      <c r="F296" s="5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Basic and diluted                                                                    $(0.01)            $0.00</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" s="5" t="n">
+        <v>230.128052</v>
+      </c>
+      <c r="F297" s="5" t="n">
+        <v>255.985803</v>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Basic and diluted                                                                    $(0.01)            $0.00</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Basic and diluted                                                                    $(0.01)            $0.00 total</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" s="5" t="n">
+        <v>0.066454</v>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
           <t>$                                                                                                                                  28,711,855                                                                                                                                                                 28,502,461                                                        (2,601,251)                 26,091,699                                            Total</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr">
+      <c r="C299" t="inlineStr">
         <is>
           <t>$                                                                                                                                                            (24,026,201)                                                     98,114                               (381,999)                     (24,310,086)                          156,001     (2,601,251)                     (26,755,336)                                                             Deficit</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
-      <c r="E286" s="5" t="n">
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" s="5" t="n">
         <v>5.995645</v>
       </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O286" t="inlineStr">
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
         <is>
           <t>-</t>
         </is>
